--- a/data/副本个股收益可视化分析包_v3b_cleaned.xlsx
+++ b/data/副本个股收益可视化分析包_v3b_cleaned.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/j/stock-dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D902317D-13BB-9949-B21A-B4F6D90D7957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD740187-237D-B24A-B480-0AC222B49770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="27120" windowHeight="16520" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12398,7 +12398,7 @@
         <v>184</v>
       </c>
       <c r="E2" s="32">
-        <v>0.1099</v>
+        <v>1000</v>
       </c>
       <c r="F2" s="32">
         <v>0.11070000000000001</v>

--- a/data/副本个股收益可视化分析包_v3b_cleaned.xlsx
+++ b/data/副本个股收益可视化分析包_v3b_cleaned.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/j/stock-dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD740187-237D-B24A-B480-0AC222B49770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA91CDF7-69BD-2E44-8493-C6ECEC8B3572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="27120" windowHeight="16520" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12398,7 +12398,7 @@
         <v>184</v>
       </c>
       <c r="E2" s="32">
-        <v>1000</v>
+        <v>0.1099</v>
       </c>
       <c r="F2" s="32">
         <v>0.11070000000000001</v>

--- a/data/副本个股收益可视化分析包_v3b_cleaned.xlsx
+++ b/data/副本个股收益可视化分析包_v3b_cleaned.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/j/stock-dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA91CDF7-69BD-2E44-8493-C6ECEC8B3572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD8C059A-8941-E449-9D39-1C63C5637EE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="27120" windowHeight="16520" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12398,7 +12398,7 @@
         <v>184</v>
       </c>
       <c r="E2" s="32">
-        <v>0.1099</v>
+        <v>1000</v>
       </c>
       <c r="F2" s="32">
         <v>0.11070000000000001</v>

--- a/data/副本个股收益可视化分析包_v3b_cleaned.xlsx
+++ b/data/副本个股收益可视化分析包_v3b_cleaned.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/j/stock-dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD8C059A-8941-E449-9D39-1C63C5637EE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B499E55E-A354-B848-8B4D-B544039FCBED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="27120" windowHeight="16520" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12398,7 +12398,7 @@
         <v>184</v>
       </c>
       <c r="E2" s="32">
-        <v>1000</v>
+        <v>0.1099</v>
       </c>
       <c r="F2" s="32">
         <v>0.11070000000000001</v>
